--- a/analise_eua/tecnologia/apple/aapl_10q.xlsx
+++ b/analise_eua/tecnologia/apple/aapl_10q.xlsx
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,13 +51,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,1729 +434,1877 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T27"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46109</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46018</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45836</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45745</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45654</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45472</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45381</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45290</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45108</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45017</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>44926</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44737</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44646</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44555</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44373</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44282</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44191</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44009</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>43918</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43827</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Cash and Cash Equivalents</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>45572</v>
+      </c>
+      <c r="C2" t="n">
         <v>45317</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>36269</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>28162</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>30299</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>25565</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>32695</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>40760</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>28408</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>24687</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>20535</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>27502</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>28098</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>37119</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>34050</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>38466</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>36010</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>33383</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>40174</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>39771</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Marketable Securities, Current</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>22935</v>
+      </c>
+      <c r="C3" t="n">
         <v>21590</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>19103</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>20336</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>23476</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>36236</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>34455</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>32340</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>34074</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>31185</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>30820</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>20729</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>23413</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>26794</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>27646</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>31368</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>40816</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>59642</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>53877</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>67391</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Accounts Receivable, after Allowance for Credit Loss, Current</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>30339</v>
+      </c>
+      <c r="C4" t="n">
         <v>39921</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>27557</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>26136</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>29639</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>22795</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>21837</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>23194</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>19549</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>17936</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>23752</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>21803</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>20815</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>30213</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>17475</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>18503</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>27101</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>17882</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>15722</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>20970</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Nontrade Receivables, Current</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>23172</v>
+      </c>
+      <c r="C5" t="n">
         <v>30399</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>19278</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>23662</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>29667</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>20377</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>19313</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>26908</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>19637</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>17963</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>30428</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>20439</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>24585</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>35040</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>16433</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>14533</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>31519</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>14193</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>14955</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>18976</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Inventory, Net</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>6747</v>
+      </c>
+      <c r="C6" t="n">
         <v>5875</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>5925</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>6269</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>6911</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>6165</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>6232</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>6511</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>7351</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>7482</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>6820</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>5433</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>5460</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>5876</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>5178</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>5219</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>4973</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>3978</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>3334</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>4097</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Other Assets, Current</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>15349</v>
+      </c>
+      <c r="C7" t="n">
         <v>15002</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>14359</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>14109</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>13248</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>14297</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>13884</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>13979</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>13640</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>13660</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>16422</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>16386</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>15809</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>18112</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>13641</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>13376</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>13687</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>10987</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>15691</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>12026</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Assets, Current</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>144114</v>
+      </c>
+      <c r="C8" t="n">
         <v>158104</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>122491</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>118674</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>133240</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>125435</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>128416</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>143692</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>122659</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>112913</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>128777</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>112292</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>118180</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>153154</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>114423</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>121465</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>154106</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>140065</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>143753</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>163231</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Marketable Securities, Noncurrent</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>78088</v>
+      </c>
+      <c r="C9" t="n">
         <v>77888</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>77614</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>84424</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>87593</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>91240</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>95187</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>99475</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>104061</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>110461</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>114095</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>131077</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>141219</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>138683</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>131948</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>134539</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>118745</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>100592</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>98793</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>99899</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Property, Plant and Equipment, Net</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>50116</v>
+      </c>
+      <c r="C10" t="n">
         <v>50159</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>48508</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>46876</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>46069</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>44502</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>43546</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>43666</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>43550</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>43398</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>42951</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>40335</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>39304</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>39245</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>38615</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>37815</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>37933</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>35687</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>35889</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>37031</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>aapl_IntangibleAssetsNetExcludingGoodwillNoncurrent</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>21334</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Other Assets, Noncurrent</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B12" t="n">
+        <v>77430</v>
+      </c>
+      <c r="C12" t="n">
         <v>93146</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D12" t="n">
         <v>82882</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E12" t="n">
         <v>81259</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F12" t="n">
         <v>77183</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G12" t="n">
         <v>70435</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H12" t="n">
         <v>70262</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I12" t="n">
         <v>66681</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J12" t="n">
         <v>64768</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K12" t="n">
         <v>65388</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L12" t="n">
         <v>60924</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M12" t="n">
         <v>52605</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N12" t="n">
         <v>51959</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O12" t="n">
         <v>50109</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P12" t="n">
         <v>44854</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q12" t="n">
         <v>43339</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R12" t="n">
         <v>43270</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S12" t="n">
         <v>41000</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T12" t="n">
         <v>41965</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U12" t="n">
         <v>40457</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Assets, Noncurrent</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B13" t="n">
+        <v>226968</v>
+      </c>
+      <c r="C13" t="n">
         <v>221193</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D13" t="n">
         <v>209004</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E13" t="n">
         <v>212559</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F13" t="n">
         <v>210845</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G13" t="n">
         <v>206177</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H13" t="n">
         <v>208995</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I13" t="n">
         <v>209822</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J13" t="n">
         <v>212379</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K13" t="n">
         <v>219247</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L13" t="n">
         <v>217970</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M13" t="n">
         <v>224017</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N13" t="n">
         <v>232482</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O13" t="n">
         <v>228037</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P13" t="n">
         <v>215417</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q13" t="n">
         <v>215693</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R13" t="n">
         <v>199948</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S13" t="n">
         <v>177279</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T13" t="n">
         <v>176647</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U13" t="n">
         <v>177387</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B14" t="n">
+        <v>371082</v>
+      </c>
+      <c r="C14" t="n">
         <v>379297</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D14" t="n">
         <v>331495</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E14" t="n">
         <v>331233</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F14" t="n">
         <v>344085</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G14" t="n">
         <v>331612</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H14" t="n">
         <v>337411</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I14" t="n">
         <v>353514</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J14" t="n">
         <v>335038</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K14" t="n">
         <v>332160</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L14" t="n">
         <v>346747</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M14" t="n">
         <v>336309</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N14" t="n">
         <v>350662</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O14" t="n">
         <v>381191</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P14" t="n">
         <v>329840</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q14" t="n">
         <v>337158</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R14" t="n">
         <v>354054</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S14" t="n">
         <v>317344</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T14" t="n">
         <v>320400</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U14" t="n">
         <v>340618</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Accounts Payable, Current</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B15" t="n">
+        <v>57349</v>
+      </c>
+      <c r="C15" t="n">
         <v>70587</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D15" t="n">
         <v>50374</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E15" t="n">
         <v>54126</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F15" t="n">
         <v>61910</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G15" t="n">
         <v>47574</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H15" t="n">
         <v>45753</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I15" t="n">
         <v>58146</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J15" t="n">
         <v>46699</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K15" t="n">
         <v>42945</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L15" t="n">
         <v>57918</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M15" t="n">
         <v>48343</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N15" t="n">
         <v>52682</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O15" t="n">
         <v>74362</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P15" t="n">
         <v>40409</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q15" t="n">
         <v>40127</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R15" t="n">
         <v>63846</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S15" t="n">
         <v>35325</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T15" t="n">
         <v>32421</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U15" t="n">
         <v>45111</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Other Liabilities, Current</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B16" t="n">
+        <v>57654</v>
+      </c>
+      <c r="C16" t="n">
         <v>68543</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D16" t="n">
         <v>62499</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E16" t="n">
         <v>61849</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F16" t="n">
         <v>61151</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G16" t="n">
         <v>60889</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H16" t="n">
         <v>57298</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I16" t="n">
         <v>54611</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J16" t="n">
         <v>58897</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K16" t="n">
         <v>56425</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L16" t="n">
         <v>59893</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M16" t="n">
         <v>48811</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N16" t="n">
         <v>50248</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O16" t="n">
         <v>49167</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P16" t="n">
         <v>43625</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q16" t="n">
         <v>45660</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R16" t="n">
         <v>48504</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S16" t="n">
         <v>35005</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T16" t="n">
         <v>37324</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U16" t="n">
         <v>36263</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Contract with Customer, Liability, Current</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B17" t="n">
+        <v>9331</v>
+      </c>
+      <c r="C17" t="n">
         <v>9413</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D17" t="n">
         <v>8979</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E17" t="n">
         <v>8976</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F17" t="n">
         <v>8461</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G17" t="n">
         <v>8053</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H17" t="n">
         <v>8012</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I17" t="n">
         <v>8264</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J17" t="n">
         <v>8158</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K17" t="n">
         <v>8131</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L17" t="n">
         <v>7992</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M17" t="n">
         <v>7728</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N17" t="n">
         <v>7920</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O17" t="n">
         <v>7876</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P17" t="n">
         <v>7681</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q17" t="n">
         <v>7595</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R17" t="n">
         <v>7395</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S17" t="n">
         <v>6313</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T17" t="n">
         <v>5928</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U17" t="n">
         <v>5573</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Commercial Paper</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B18" t="n">
         <v>1997</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C18" t="n">
+        <v>1997</v>
+      </c>
+      <c r="D18" t="n">
         <v>9923</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E18" t="n">
         <v>5982</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F18" t="n">
         <v>1995</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G18" t="n">
         <v>2994</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H18" t="n">
         <v>1997</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I18" t="n">
         <v>1998</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J18" t="n">
         <v>3993</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K18" t="n">
         <v>1996</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L18" t="n">
         <v>1743</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M18" t="n">
         <v>10982</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N18" t="n">
         <v>6999</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O18" t="n">
         <v>5000</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P18" t="n">
         <v>8000</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q18" t="n">
         <v>5000</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R18" t="n">
         <v>5000</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S18" t="n">
         <v>11166</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T18" t="n">
         <v>10029</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U18" t="n">
         <v>4990</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Long-term Debt, Current</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B19" t="n">
+        <v>8310</v>
+      </c>
+      <c r="C19" t="n">
         <v>11827</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D19" t="n">
         <v>9345</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E19" t="n">
         <v>13638</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F19" t="n">
         <v>10848</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G19" t="n">
         <v>12114</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H19" t="n">
         <v>10762</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I19" t="n">
         <v>10954</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J19" t="n">
         <v>7216</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K19" t="n">
         <v>10578</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L19" t="n">
         <v>9740</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M19" t="n">
         <v>14009</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N19" t="n">
         <v>9659</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O19" t="n">
         <v>11169</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P19" t="n">
         <v>8039</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q19" t="n">
         <v>8003</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R19" t="n">
         <v>7762</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S19" t="n">
         <v>7509</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T19" t="n">
         <v>10392</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U19" t="n">
         <v>10224</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Liabilities, Current</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B20" t="n">
+        <v>134641</v>
+      </c>
+      <c r="C20" t="n">
         <v>162367</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D20" t="n">
         <v>141120</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E20" t="n">
         <v>144571</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F20" t="n">
         <v>144365</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G20" t="n">
         <v>131624</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H20" t="n">
         <v>123822</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I20" t="n">
         <v>133973</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J20" t="n">
         <v>124963</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K20" t="n">
         <v>120075</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L20" t="n">
         <v>137286</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M20" t="n">
         <v>129873</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N20" t="n">
         <v>127508</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O20" t="n">
         <v>147574</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P20" t="n">
         <v>107754</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q20" t="n">
         <v>106385</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R20" t="n">
         <v>132507</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S20" t="n">
         <v>95318</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T20" t="n">
         <v>96094</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U20" t="n">
         <v>102161</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Long-term Debt, Noncurrent</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B21" t="n">
+        <v>74404</v>
+      </c>
+      <c r="C21" t="n">
         <v>76685</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D21" t="n">
         <v>82430</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E21" t="n">
         <v>78566</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F21" t="n">
         <v>83956</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G21" t="n">
         <v>86196</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H21" t="n">
         <v>91831</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I21" t="n">
         <v>95088</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J21" t="n">
         <v>98071</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K21" t="n">
         <v>97041</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L21" t="n">
         <v>99627</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M21" t="n">
         <v>94700</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N21" t="n">
         <v>103323</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O21" t="n">
         <v>106629</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P21" t="n">
         <v>105752</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q21" t="n">
         <v>108642</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R21" t="n">
         <v>99281</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S21" t="n">
         <v>94048</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T21" t="n">
         <v>89086</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U21" t="n">
         <v>93078</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Other Liabilities, Noncurrent</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
+        <v>55546</v>
+      </c>
+      <c r="C22" t="n">
         <v>52055</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D22" t="n">
         <v>42115</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E22" t="n">
         <v>41300</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F22" t="n">
         <v>49006</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G22" t="n">
         <v>47084</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H22" t="n">
         <v>47564</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I22" t="n">
         <v>50353</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J22" t="n">
         <v>51730</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K22" t="n">
         <v>52886</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L22" t="n">
         <v>53107</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M22" t="n">
         <v>53629</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N22" t="n">
         <v>52432</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O22" t="n">
         <v>55056</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P22" t="n">
         <v>52054</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q22" t="n">
         <v>52953</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R22" t="n">
         <v>56042</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S22" t="n">
         <v>55696</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T22" t="n">
         <v>56795</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U22" t="n">
         <v>55848</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Liabilities, Noncurrent</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B23" t="n">
+        <v>129950</v>
+      </c>
+      <c r="C23" t="n">
         <v>128740</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D23" t="n">
         <v>124545</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E23" t="n">
         <v>119866</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F23" t="n">
         <v>132962</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G23" t="n">
         <v>133280</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H23" t="n">
         <v>139395</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I23" t="n">
         <v>145441</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J23" t="n">
         <v>149801</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K23" t="n">
         <v>149927</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L23" t="n">
         <v>152734</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M23" t="n">
         <v>148329</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N23" t="n">
         <v>155755</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O23" t="n">
         <v>161685</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P23" t="n">
         <v>157806</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q23" t="n">
         <v>161595</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R23" t="n">
         <v>155323</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S23" t="n">
         <v>149744</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T23" t="n">
         <v>145881</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U23" t="n">
         <v>148926</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Liabilities</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B24" t="n">
+        <v>264591</v>
+      </c>
+      <c r="C24" t="n">
         <v>291107</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D24" t="n">
         <v>265665</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E24" t="n">
         <v>264437</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F24" t="n">
         <v>277327</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G24" t="n">
         <v>264904</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H24" t="n">
         <v>263217</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I24" t="n">
         <v>279414</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J24" t="n">
         <v>274764</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K24" t="n">
         <v>270002</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L24" t="n">
         <v>290020</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M24" t="n">
         <v>278202</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N24" t="n">
         <v>283263</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O24" t="n">
         <v>309259</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P24" t="n">
         <v>265560</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q24" t="n">
         <v>267980</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R24" t="n">
         <v>287830</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S24" t="n">
         <v>245062</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T24" t="n">
         <v>241975</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U24" t="n">
         <v>251087</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Common Stocks, Including Additional Paid in Capital</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B25" t="n">
+        <v>99507</v>
+      </c>
+      <c r="C25" t="n">
         <v>95221</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D25" t="n">
         <v>89806</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E25" t="n">
         <v>88711</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F25" t="n">
         <v>84768</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G25" t="n">
         <v>79850</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H25" t="n">
         <v>78815</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I25" t="n">
         <v>75236</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J25" t="n">
         <v>70667</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K25" t="n">
         <v>69568</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L25" t="n">
         <v>66399</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M25" t="n">
         <v>62115</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N25" t="n">
         <v>61181</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O25" t="n">
         <v>58424</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P25" t="n">
         <v>54989</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q25" t="n">
         <v>54203</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R25" t="n">
         <v>51744</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S25" t="n">
         <v>48696</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T25" t="n">
         <v>48032</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U25" t="n">
         <v>45972</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Retained Earnings (Accumulated Deficit)</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B26" t="n">
+        <v>12359</v>
+      </c>
+      <c r="C26" t="n">
         <v>-2177</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D26" t="n">
         <v>-17607</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E26" t="n">
         <v>-15552</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F26" t="n">
         <v>-11221</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G26" t="n">
         <v>-4726</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H26" t="n">
         <v>4339</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I26" t="n">
         <v>8242</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J26" t="n">
         <v>1408</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K26" t="n">
         <v>4336</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L26" t="n">
         <v>3240</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M26" t="n">
         <v>5289</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N26" t="n">
         <v>12712</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O26" t="n">
         <v>14435</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P26" t="n">
         <v>9233</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q26" t="n">
         <v>15261</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R26" t="n">
         <v>14301</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S26" t="n">
         <v>24136</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T26" t="n">
         <v>33182</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U26" t="n">
         <v>43977</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Accumulated Other Comprehensive Income (Loss), Net of Tax</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B27" t="n">
+        <v>-5375</v>
+      </c>
+      <c r="C27" t="n">
         <v>-4854</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D27" t="n">
         <v>-6369</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E27" t="n">
         <v>-6363</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F27" t="n">
         <v>-6789</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G27" t="n">
         <v>-8416</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H27" t="n">
         <v>-8960</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I27" t="n">
         <v>-9378</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J27" t="n">
         <v>-11801</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K27" t="n">
         <v>-11746</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L27" t="n">
         <v>-12912</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M27" t="n">
         <v>-9297</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N27" t="n">
         <v>-6494</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O27" t="n">
         <v>-927</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P27" t="n">
         <v>58</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q27" t="n">
         <v>-286</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R27" t="n">
         <v>179</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S27" t="n">
         <v>-550</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T27" t="n">
         <v>-2789</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U27" t="n">
         <v>-418</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Total Shareholders Equity</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B28" t="n">
+        <v>106491</v>
+      </c>
+      <c r="C28" t="n">
         <v>88190</v>
       </c>
-      <c r="C27" t="n">
+      <c r="D28" t="n">
         <v>65830</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E28" t="n">
         <v>66796</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F28" t="n">
         <v>66758</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G28" t="n">
         <v>66708</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H28" t="n">
         <v>74194</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I28" t="n">
         <v>74100</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J28" t="n">
         <v>60274</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K28" t="n">
         <v>62158</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L28" t="n">
         <v>56727</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M28" t="n">
         <v>58107</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N28" t="n">
         <v>67399</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O28" t="n">
         <v>71932</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P28" t="n">
         <v>64280</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q28" t="n">
         <v>69178</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R28" t="n">
         <v>66224</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S28" t="n">
         <v>72282</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T28" t="n">
         <v>78425</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U28" t="n">
         <v>89531</v>
       </c>
     </row>
@@ -2157,1025 +2319,1073 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46109</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46018</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45836</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45745</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45654</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45472</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45381</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45290</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45108</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45017</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>44926</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44737</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44646</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44555</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44373</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44282</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44191</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44009</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>43918</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43827</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Revenues</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>111184</v>
+      </c>
+      <c r="C2" t="n">
         <v>143756</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>94036</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>95359</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>124300</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>85777</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>90753</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>119575</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>81797</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>94836</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>117154</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>82959</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>97278</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>123945</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>81434</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>89584</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>111439</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>59685</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>58313</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>91819</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Cost of Goods and Services Sold</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>56403</v>
+      </c>
+      <c r="C3" t="n">
         <v>74525</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>50318</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>50492</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>66025</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>46099</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>48482</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>64720</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>45384</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>52860</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>66822</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>47074</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>54719</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>69702</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>46179</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>51505</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>67111</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>37005</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>35943</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>56602</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>54781</v>
+      </c>
+      <c r="C4" t="n">
         <v>69231</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>43718</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>44867</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>58275</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>39678</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>42271</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>54855</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>36413</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>41976</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>50332</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>35885</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>42559</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>54243</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>35255</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>38079</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>44328</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>22680</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>22370</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>35217</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Research and Development</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>11419</v>
+      </c>
+      <c r="C5" t="n">
         <v>10887</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>8866</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>8550</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>8268</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>8006</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>7903</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>7696</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>7442</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>7457</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>7709</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>6797</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>6387</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>6306</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>5717</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>5262</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>5163</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>4758</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>4565</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>4451</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Selling, General and Administrative Expense</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>7477</v>
+      </c>
+      <c r="C6" t="n">
         <v>7492</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>6650</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>6728</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>7175</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>6320</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>6468</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>6786</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>5973</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>6201</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>6607</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>6012</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>6193</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>6449</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>5412</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>5314</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>5631</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>4831</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>4952</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>5197</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Operating Expenses</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>18896</v>
+      </c>
+      <c r="C7" t="n">
         <v>18379</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>15516</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>15278</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>15443</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>14326</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>14371</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>14482</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>13415</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>13658</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>14316</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>12809</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>12580</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>12755</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>11129</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>10576</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>10794</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>9589</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>9517</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>9648</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Operating Income</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>35885</v>
+      </c>
+      <c r="C8" t="n">
         <v>50852</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>28202</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>29589</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>42832</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>25352</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>27900</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>40373</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>22998</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>28318</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>36016</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>23076</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>29979</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>41488</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>24126</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>27503</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>33534</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>13091</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>12853</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>25569</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Nonoperating Income (Expense)</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>-52</v>
+      </c>
+      <c r="C9" t="n">
         <v>150</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>-171</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>-279</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>-248</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>142</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>158</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>-50</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>-265</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>64</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>-393</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>-10</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>160</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>-247</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>243</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>508</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>45</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>46</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>282</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>349</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Income Before Provision for Income Taxes</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>35833</v>
+      </c>
+      <c r="C10" t="n">
         <v>51002</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>28031</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>29310</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>42584</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>25494</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>28058</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>40323</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>22733</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>28382</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>35623</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>23066</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>30139</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>41241</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>24369</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>28011</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>33579</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>13137</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>13135</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>25918</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Provision for Income Taxes</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>6255</v>
+      </c>
+      <c r="C11" t="n">
         <v>8905</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>4597</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>4530</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>6254</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>4046</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>4422</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>6407</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>2852</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>4222</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>5625</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>3624</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>5129</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>6611</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>2625</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>4381</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>4824</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>1884</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>1886</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>3682</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>29578</v>
+      </c>
+      <c r="C12" t="n">
         <v>42097</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>23434</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>24780</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>36330</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>21448</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>23636</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>33916</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>19881</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>24160</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>29998</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>19442</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>25010</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>34630</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>21744</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>23630</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>28755</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>11253</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>11249</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>22236</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Earnings Per Share, Basic</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="C13" t="n">
         <v>2.85</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>1.57</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>1.65</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>2.41</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>1.4</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>1.53</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>2.19</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>1.27</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>1.53</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>1.89</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>1.2</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>1.54</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>2.11</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>1.31</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>1.41</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>1.7</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>2.61</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>2.58</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>5.04</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Earnings Per Share, Diluted</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="C14" t="n">
         <v>2.84</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>1.57</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>1.65</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>2.4</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>1.4</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>1.53</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>2.18</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>1.26</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>1.52</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>1.88</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>1.2</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>1.52</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>2.1</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>1.3</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>1.68</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>2.58</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>2.55</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>4.99</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Number of Shares - Basic</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>14673278</v>
+      </c>
+      <c r="C15" t="n">
         <v>14748158</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>14902886</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>14994082</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>15081724</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>15287521</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>15405856</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>15509763</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>15697614</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>15787154</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>15892723</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>16162945</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>16278802</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>16391724</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>16629371</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>16753476</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>16935119</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>4312573</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>4360101</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>4415040</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Number of Shares - Diluted</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>14725873</v>
+      </c>
+      <c r="C16" t="n">
         <v>14810356</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>14948179</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>15056133</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>15150865</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>15348175</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>15464709</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>15576641</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>15775021</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>15847050</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>15955718</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>16262203</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16403316</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>16519291</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>16781735</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>16929157</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>17113688</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>4354788</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>4404691</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>4454604</v>
       </c>
     </row>
@@ -3190,70 +3400,73 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T37"/>
+  <dimension ref="A1:U37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46109</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46018</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45836</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45745</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45654</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45472</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45381</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45290</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45108</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45017</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>44926</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44737</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44646</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44555</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44373</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44282</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44191</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44009</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>43918</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43827</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents</t>
         </is>
@@ -3262,7 +3475,7 @@
         <v>35934</v>
       </c>
       <c r="C2" t="n">
-        <v>29943</v>
+        <v>35934</v>
       </c>
       <c r="D2" t="n">
         <v>29943</v>
@@ -3271,7 +3484,7 @@
         <v>29943</v>
       </c>
       <c r="F2" t="n">
-        <v>30737</v>
+        <v>29943</v>
       </c>
       <c r="G2" t="n">
         <v>30737</v>
@@ -3280,7 +3493,7 @@
         <v>30737</v>
       </c>
       <c r="I2" t="n">
-        <v>24977</v>
+        <v>30737</v>
       </c>
       <c r="J2" t="n">
         <v>24977</v>
@@ -3289,7 +3502,7 @@
         <v>24977</v>
       </c>
       <c r="L2" t="n">
-        <v>35929</v>
+        <v>24977</v>
       </c>
       <c r="M2" t="n">
         <v>35929</v>
@@ -3298,7 +3511,7 @@
         <v>35929</v>
       </c>
       <c r="O2" t="n">
-        <v>39789</v>
+        <v>35929</v>
       </c>
       <c r="P2" t="n">
         <v>39789</v>
@@ -3307,7 +3520,7 @@
         <v>39789</v>
       </c>
       <c r="R2" t="n">
-        <v>50224</v>
+        <v>39789</v>
       </c>
       <c r="S2" t="n">
         <v>50224</v>
@@ -3315,1673 +3528,1754 @@
       <c r="T2" t="n">
         <v>50224</v>
       </c>
+      <c r="U2" t="n">
+        <v>50224</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Net Income (Loss) Attributable to Parent</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>71675</v>
+      </c>
+      <c r="C3" t="n">
         <v>42097</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>84544</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>61110</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>36330</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>79000</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>57552</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>33916</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>74039</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>54158</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>29998</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>79082</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>59640</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>34630</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>74129</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>52385</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>28755</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>44738</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>33485</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>22236</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Depreciation, Depletion and Amortization</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>6653</v>
+      </c>
+      <c r="C4" t="n">
         <v>3214</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>8571</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>5741</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>3080</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>8534</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>5684</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>2848</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>8866</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>5814</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>2916</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>8239</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>5434</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>2697</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>8295</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>5463</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>2666</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>8354</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>5602</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>2816</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Share-based Payment Arrangement, Noncash Expense</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>7122</v>
+      </c>
+      <c r="C5" t="n">
         <v>3594</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>9680</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>6512</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>3286</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>8830</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>5961</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>2997</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>8208</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>5591</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>2905</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>6760</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>4517</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>2265</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>5961</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>4001</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>2020</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>5105</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>3407</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>1710</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Other Noncash Income (Expense)</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>-1717</v>
+      </c>
+      <c r="C6" t="n">
         <v>-528</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>-1748</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>-2217</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>-2009</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>-1964</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>-1971</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>-989</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>-1651</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>-1732</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>-317</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>-61</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>-20</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>167</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>-689</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>-474</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>25</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>-94</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>-259</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>-142</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Accounts Receivable</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>9295</v>
+      </c>
+      <c r="C7" t="n">
         <v>-153</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>5685</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>7266</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>3597</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>6697</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>7727</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>6555</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>7609</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>9596</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>4275</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>4561</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>5542</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>-3934</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>-1316</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>-2347</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>-10945</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>5149</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>7284</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>2015</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Other Receivables</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>10008</v>
+      </c>
+      <c r="C8" t="n">
         <v>2781</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>13555</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>9171</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>3166</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>11100</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>12164</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>4569</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>13111</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>14785</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>2320</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>4789</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>643</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>-9812</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>4892</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>6792</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>-10194</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>8685</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>7923</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>3902</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Inventories</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>-1084</v>
+      </c>
+      <c r="C9" t="n">
         <v>-211</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>1223</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>858</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>215</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>41</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>53</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>-137</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>-2570</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>-2548</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>-1807</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>1049</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>1065</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>681</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>-1213</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>-1226</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>-950</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>10</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>699</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>-28</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Other Operating Assets</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>-14329</v>
+      </c>
+      <c r="C10" t="n">
         <v>-10250</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>-6116</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>-4371</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>939</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>-5626</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>-4438</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>-1457</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>-4863</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>-4092</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>-4099</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>-3289</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>-3542</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>-4921</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>-5899</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>-4333</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>-3526</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>-6760</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>-8866</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>-7054</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Accounts Payable</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>-12297</v>
+      </c>
+      <c r="C11" t="n">
         <v>848</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>-18479</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>-14604</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>-6671</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>-15171</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>-16710</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>-4542</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>-16790</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>-20764</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>-6075</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>-6108</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>-1750</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>19813</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>-1786</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>-1997</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>21670</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>-10787</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>-13520</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>-1089</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Other Operating Liabilities</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>7301</v>
+      </c>
+      <c r="C12" t="n">
         <v>12533</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>-15161</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>-15579</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>-11998</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>2</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>-3437</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>-3865</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>2986</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>1757</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>3758</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>-14</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>1888</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>4236</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>463</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>3045</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>7959</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>3867</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>7500</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>5514</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Net Cash Provided by (Used in) Operating Activities</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>82627</v>
+      </c>
+      <c r="C13" t="n">
         <v>53925</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>81754</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>53887</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>29935</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>91443</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>62585</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>39895</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>88945</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>62565</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>34005</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>98024</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>75132</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>46966</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>83838</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>62744</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>38763</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>60098</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>43827</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>30516</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Payments to Acquire Debt Securities, Available-for-sale</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>-32432</v>
+      </c>
+      <c r="C14" t="n">
         <v>-12693</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>-17591</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>-12442</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>-6124</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>-38074</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>-25042</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>-9780</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>-20956</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>-11197</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>-5153</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>-70178</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>-61987</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>-34913</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>-94052</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>-74424</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>-39800</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>-96606</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>-66489</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>-37416</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Proceeds from Maturities, Prepayments and Calls of Debt Securities, Available-for-sale</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>18691</v>
+      </c>
+      <c r="C15" t="n">
         <v>7510</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>35036</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>26587</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>15967</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>39838</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>27462</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>13046</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>27857</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>17124</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>7127</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>24203</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>18000</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>11309</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>49880</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>39605</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>25177</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>54865</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>39738</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>19740</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Proceeds from Sale of Debt Securities, Available-for-sale</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>8615</v>
+      </c>
+      <c r="C16" t="n">
         <v>2824</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>10785</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>5210</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>3492</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>7382</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>4314</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>1337</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>3959</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>1897</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>509</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>33609</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>24668</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>10675</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>36745</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>21645</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>9344</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>39760</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>27762</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>7280</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Purchases Of Property And Equipment And Intangible Assets</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>-4344</v>
+      </c>
+      <c r="C17" t="n">
         <v>-2373</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>-9473</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>-6011</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>-2940</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>-6539</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>-4388</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>-2392</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>-8796</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>-6703</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>-3787</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>-7419</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>-5317</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>-2803</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>-7862</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>-5769</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>-3500</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>-5525</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>-3960</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>-2107</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Payments for (Proceeds from) Other Investing Activities</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>-1584</v>
+      </c>
+      <c r="C18" t="n">
         <v>-154</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>-975</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>-635</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>-603</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>-1117</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>-729</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>-284</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>-753</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>-247</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>-141</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>-1183</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>-568</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>-374</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>-78</v>
       </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
       <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
         <v>204</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>-689</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>-426</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>-130</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Net Cash Provided by (Used in) Investing Activities</t>
         </is>
       </c>
       <c r="B19" t="n">
+        <v>-11054</v>
+      </c>
+      <c r="C19" t="n">
         <v>-4886</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>17782</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>12709</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>9792</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>1490</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>1617</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>1927</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1311</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>874</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>-1445</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>-21137</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>-25371</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>-16106</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>-15380</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>-18952</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>-8584</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>-9820</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>-4655</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>-13668</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Payment, Tax Withholding, Share-based Payment Arrangement</t>
         </is>
       </c>
       <c r="B20" t="n">
+        <v>-3252</v>
+      </c>
+      <c r="C20" t="n">
         <v>-2922</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>-5719</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>-3205</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>-2921</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>-5163</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>-2875</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>-2591</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>-5119</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>-2734</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>-2316</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>-5915</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>-3218</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>-2888</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>-5855</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>-3160</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>-2861</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>-3234</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>-1566</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>-1379</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Payments of Dividends</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>-7743</v>
+      </c>
+      <c r="C21" t="n">
         <v>-3921</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>-11559</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>-7614</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>-3856</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>-11430</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>-7535</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>-3825</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>-11267</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>-7418</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>-3768</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>-11138</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>-7327</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>-3732</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>-10827</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>-7060</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>-3613</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>-10570</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>-6914</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>-3539</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Payments for Repurchase of Common Stock</t>
         </is>
       </c>
       <c r="B22" t="n">
+        <v>-36989</v>
+      </c>
+      <c r="C22" t="n">
         <v>-24701</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>-70579</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>-49504</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>-23606</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>-69866</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>-43344</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>-20139</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>-56547</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>-39069</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>-19475</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>-64974</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>-43109</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>-20478</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>-66223</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>-43323</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>-24775</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>-55171</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>-39280</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>-20706</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Repayments of Long-term Debt</t>
         </is>
       </c>
       <c r="B23" t="n">
+        <v>-7914</v>
+      </c>
+      <c r="C23" t="n">
         <v>-2164</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>-9682</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>-4009</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>-1009</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>-7400</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>-3150</v>
       </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
       <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
         <v>-11151</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>-3651</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>-1401</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>-6750</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>-3750</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
       <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
         <v>-7500</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>-4500</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>-1000</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>-12629</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>-5250</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>-1000</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Proceeds from (Repayments of) Commercial Paper</t>
         </is>
       </c>
       <c r="B24" t="n">
+        <v>-5911</v>
+      </c>
+      <c r="C24" t="n">
         <v>-5910</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>-65</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>-3968</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>-7944</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>-2985</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>-3982</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>-3984</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>-5971</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>-7960</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>-8214</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>4970</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>999</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>-1000</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>3022</v>
-      </c>
-      <c r="P24" t="n">
-        <v>22</v>
       </c>
       <c r="Q24" t="n">
         <v>22</v>
       </c>
       <c r="R24" t="n">
+        <v>22</v>
+      </c>
+      <c r="S24" t="n">
         <v>31</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>1518</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>-979</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Proceeds from (Payments for) Other Financing Activities</t>
         </is>
       </c>
       <c r="B25" t="n">
+        <v>-126</v>
+      </c>
+      <c r="C25" t="n">
         <v>-38</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>-87</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>-77</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>-35</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>-191</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>-132</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>-46</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>-508</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>-455</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>-389</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>-148</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>-105</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>-61</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>-72</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>-38</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>-22</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>-120</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>-51</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>-16</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Net Cash Provided by (Used in) Financing Activities</t>
         </is>
       </c>
       <c r="B26" t="n">
+        <v>-61935</v>
+      </c>
+      <c r="C26" t="n">
         <v>-39656</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>-93210</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>-68377</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>-39371</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>-97035</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>-61018</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>-30585</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>-85335</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>-61287</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>-35563</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>-83955</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>-56510</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>-28159</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>-72971</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>-43575</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>-32249</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>-65463</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>-46347</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>-25407</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Period Increase (Decrease), Including Exchange Rate Effect</t>
         </is>
       </c>
       <c r="B27" t="n">
+        <v>9638</v>
+      </c>
+      <c r="C27" t="n">
         <v>9383</v>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>6326</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>-1781</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>356</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>-4102</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>3184</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>11237</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>4921</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>2152</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>-3003</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>-7068</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>-6749</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>2701</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>-4513</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>217</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>-2070</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>-15185</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>-7175</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>-8559</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Income Taxes Paid, Net</t>
         </is>
       </c>
       <c r="B28" t="n">
+        <v>20397</v>
+      </c>
+      <c r="C28" t="n">
         <v>3434</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>37332</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>31683</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>18651</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>19230</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>14531</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>7255</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>7020</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>4894</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>828</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>12251</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>9301</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>5235</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>18536</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>10276</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>1787</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>8410</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>7505</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>4393</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Proceeds from Issuance of Long-term Debt</t>
         </is>
@@ -4990,11 +5284,11 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
         <v>4481</v>
       </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
@@ -5008,11 +5302,11 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
         <v>5228</v>
       </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
@@ -5026,26 +5320,29 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>13923</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>13923</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>13923</v>
       </c>
       <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
         <v>10635</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2210</v>
       </c>
       <c r="T29" t="n">
         <v>2210</v>
       </c>
+      <c r="U29" t="n">
+        <v>2210</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Interest Paid, Excluding Capitalized Interest, Operating Activities</t>
         </is>
@@ -5072,44 +5369,47 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
         <v>2590</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>1873</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>703</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>1910</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>1406</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>531</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>1870</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>1327</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>619</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>2275</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1689</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>771</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Contract with Customer, Liability</t>
         </is>
@@ -5142,38 +5442,41 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>131</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>260</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>627</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>462</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>1738</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>1642</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>1341</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>1649</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>1223</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>985</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Deferred Income Tax Expense (Benefit)</t>
         </is>
@@ -5209,35 +5512,38 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>2756</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>1088</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>682</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>-737</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>-207</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>-58</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>182</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>-651</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>-349</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Payments to Acquire Businesses, Net of Cash Acquired</t>
         </is>
@@ -5273,35 +5579,38 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
         <v>-169</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>-167</v>
       </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
       <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
         <v>-13</v>
-      </c>
-      <c r="P33" t="n">
-        <v>-9</v>
       </c>
       <c r="Q33" t="n">
         <v>-9</v>
       </c>
       <c r="R33" t="n">
+        <v>-9</v>
+      </c>
+      <c r="S33" t="n">
         <v>-1473</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>-1134</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>-958</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Proceeds from Issuance of Common Stock</t>
         </is>
@@ -5346,26 +5655,29 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>561</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
         <v>561</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>561</v>
       </c>
       <c r="R34" t="n">
-        <v>430</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>430</v>
       </c>
       <c r="T34" t="n">
+        <v>430</v>
+      </c>
+      <c r="U34" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Proceeds from Other Short-term Debt</t>
         </is>
@@ -5419,17 +5731,20 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>5165</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>2556</v>
       </c>
-      <c r="T35" t="n">
+      <c r="U35" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Payments to Acquire Other Investments</t>
         </is>
@@ -5483,17 +5798,20 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
         <v>-210</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>-146</v>
       </c>
-      <c r="T36" t="n">
+      <c r="U36" t="n">
         <v>-77</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Proceeds from Sale and Maturity of Other Investments</t>
         </is>
@@ -5547,12 +5865,15 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
         <v>58</v>
       </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
       <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5572,17 +5893,17 @@
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
-        <v>46018</v>
+        <v>46109</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>RSUs</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>176096</v>
+        <v>173985</v>
       </c>
     </row>
   </sheetData>

--- a/analise_eua/tecnologia/apple/aapl_10q.xlsx
+++ b/analise_eua/tecnologia/apple/aapl_10q.xlsx
@@ -434,68 +434,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:V28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46109</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>46018</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45836</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45745</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45654</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45472</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45381</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45290</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45108</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45017</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44926</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44737</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44646</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44555</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44373</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44282</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44191</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44009</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43918</v>
       </c>
-      <c r="U1" s="1" t="n">
+      <c r="V1" s="1" t="n">
         <v>43827</v>
       </c>
     </row>
@@ -506,63 +509,66 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>39544</v>
+      </c>
+      <c r="C2" t="n">
         <v>45572</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>45317</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>36269</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>28162</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>30299</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>25565</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>32695</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>40760</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>28408</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>24687</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>20535</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>27502</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>28098</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>37119</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>34050</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>38466</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>36010</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>33383</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>40174</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>39771</v>
       </c>
     </row>
@@ -573,63 +579,66 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>22855</v>
+      </c>
+      <c r="C3" t="n">
         <v>22935</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>21590</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>19103</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>20336</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>23476</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>36236</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>34455</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>32340</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>34074</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>31185</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>30820</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>20729</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>23413</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>26794</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>27646</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>31368</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>40816</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>59642</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>53877</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>67391</v>
       </c>
     </row>
@@ -640,63 +649,66 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>31398</v>
+      </c>
+      <c r="C4" t="n">
         <v>30339</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>39921</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>27557</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>26136</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>29639</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>22795</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>21837</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>23194</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>19549</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>17936</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>23752</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>21803</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>20815</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>30213</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>17475</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>18503</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>27101</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>17882</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>15722</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>20970</v>
       </c>
     </row>
@@ -707,63 +719,66 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>27509</v>
+      </c>
+      <c r="C5" t="n">
         <v>23172</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>30399</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>19278</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>23662</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>29667</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>20377</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>19313</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>26908</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>19637</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>17963</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>30428</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>20439</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>24585</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>35040</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>16433</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>14533</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>31519</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>14193</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>14955</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>18976</v>
       </c>
     </row>
@@ -774,63 +789,66 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>11092</v>
+      </c>
+      <c r="C6" t="n">
         <v>6747</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>5875</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>5925</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>6269</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>6911</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>6165</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>6232</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>6511</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>7351</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>7482</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>6820</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>5433</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>5460</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>5876</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>5178</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>5219</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>4973</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>3978</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>3334</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>4097</v>
       </c>
     </row>
@@ -841,63 +859,66 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>17420</v>
+      </c>
+      <c r="C7" t="n">
         <v>15349</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>15002</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>14359</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>14109</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>13248</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>14297</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>13884</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>13979</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>13640</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>13660</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>16422</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>16386</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>15809</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>18112</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>13641</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>13376</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>13687</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>10987</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>15691</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>12026</v>
       </c>
     </row>
@@ -908,63 +929,66 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>149818</v>
+      </c>
+      <c r="C8" t="n">
         <v>144114</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>158104</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>122491</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>118674</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>133240</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>125435</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>128416</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>143692</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>122659</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>112913</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>128777</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>112292</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>118180</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>153154</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>114423</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>121465</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>154106</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>140065</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>143753</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>163231</v>
       </c>
     </row>
@@ -975,63 +999,66 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>84118</v>
+      </c>
+      <c r="C9" t="n">
         <v>78088</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>77888</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>77614</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>84424</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>87593</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>91240</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>95187</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>99475</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>104061</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>110461</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>114095</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>131077</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>141219</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>138683</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>131948</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>134539</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>118745</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>100592</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>98793</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>99899</v>
       </c>
     </row>
@@ -1042,63 +1069,66 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>51431</v>
+      </c>
+      <c r="C10" t="n">
         <v>50116</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>50159</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>48508</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>46876</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>46069</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>44502</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>43546</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>43666</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>43550</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>43398</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>42951</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>40335</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>39304</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>39245</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>38615</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>37815</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>37933</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>35687</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>35889</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>37031</v>
       </c>
     </row>
@@ -1109,11 +1139,11 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>20342</v>
+      </c>
+      <c r="C11" t="n">
         <v>21334</v>
       </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
@@ -1166,6 +1196,9 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1176,63 +1209,66 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>77557</v>
+      </c>
+      <c r="C12" t="n">
         <v>77430</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>93146</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>82882</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>81259</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>77183</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>70435</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>70262</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>66681</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>64768</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>65388</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>60924</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>52605</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>51959</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>50109</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>44854</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>43339</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>43270</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>41000</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>41965</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>40457</v>
       </c>
     </row>
@@ -1243,63 +1279,66 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>233448</v>
+      </c>
+      <c r="C13" t="n">
         <v>226968</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>221193</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>209004</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>212559</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>210845</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>206177</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>208995</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>209822</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>212379</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>219247</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>217970</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>224017</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>232482</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>228037</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>215417</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>215693</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>199948</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>177279</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>176647</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>177387</v>
       </c>
     </row>
@@ -1310,63 +1349,66 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>383266</v>
+      </c>
+      <c r="C14" t="n">
         <v>371082</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>379297</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>331495</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>331233</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>344085</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>331612</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>337411</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>353514</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>335038</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>332160</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>346747</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>336309</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>350662</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>381191</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>329840</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>337158</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>354054</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>317344</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>320400</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>340618</v>
       </c>
     </row>
@@ -1377,63 +1419,66 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>64525</v>
+      </c>
+      <c r="C15" t="n">
         <v>57349</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>70587</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>50374</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>54126</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>61910</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>47574</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>45753</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>58146</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>46699</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>42945</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>57918</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>48343</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>52682</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>74362</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>40409</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>40127</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>63846</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>35325</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>32421</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>45111</v>
       </c>
     </row>
@@ -1444,63 +1489,66 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>62259</v>
+      </c>
+      <c r="C16" t="n">
         <v>57654</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>68543</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>62499</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>61849</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>61151</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>60889</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>57298</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>54611</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>58897</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>56425</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>59893</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>48811</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>50248</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>49167</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>43625</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>45660</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>48504</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>35005</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>37324</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>36263</v>
       </c>
     </row>
@@ -1511,63 +1559,66 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>9538</v>
+      </c>
+      <c r="C17" t="n">
         <v>9331</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>9413</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>8979</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>8976</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>8461</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>8053</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>8012</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>8264</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>8158</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>8131</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>7992</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>7728</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>7920</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>7876</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>7681</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>7595</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>7395</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>6313</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>5928</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>5573</v>
       </c>
     </row>
@@ -1584,57 +1635,60 @@
         <v>1997</v>
       </c>
       <c r="D18" t="n">
+        <v>1997</v>
+      </c>
+      <c r="E18" t="n">
         <v>9923</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>5982</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>1995</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>2994</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>1997</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>1998</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>3993</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>1996</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>1743</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>10982</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>6999</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>5000</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>8000</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>5000</v>
       </c>
       <c r="R18" t="n">
         <v>5000</v>
       </c>
       <c r="S18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T18" t="n">
         <v>11166</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>10029</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>4990</v>
       </c>
     </row>
@@ -1645,63 +1699,66 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>11007</v>
+      </c>
+      <c r="C19" t="n">
         <v>8310</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>11827</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>9345</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>13638</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>10848</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>12114</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>10762</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>10954</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>7216</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>10578</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>9740</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>14009</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>9659</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>11169</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>8039</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>8003</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>7762</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7509</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>10392</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>10224</v>
       </c>
     </row>
@@ -1712,63 +1769,66 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>149326</v>
+      </c>
+      <c r="C20" t="n">
         <v>134641</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>162367</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>141120</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>144571</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>144365</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>131624</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>123822</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>133973</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>124963</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>120075</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>137286</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>129873</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>127508</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>147574</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>107754</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>106385</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>132507</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>95318</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>96094</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>102161</v>
       </c>
     </row>
@@ -1779,63 +1839,66 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>71340</v>
+      </c>
+      <c r="C21" t="n">
         <v>74404</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>76685</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>82430</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>78566</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>83956</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>86196</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>91831</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>95088</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>98071</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>97041</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>99627</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>94700</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>103323</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>106629</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>105752</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>108642</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>99281</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>94048</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>89086</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>93078</v>
       </c>
     </row>
@@ -1846,63 +1909,66 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>55080</v>
+      </c>
+      <c r="C22" t="n">
         <v>55546</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>52055</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>42115</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>41300</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>49006</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>47084</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>47564</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>50353</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>51730</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>52886</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>53107</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>53629</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>52432</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>55056</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>52054</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>52953</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>56042</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>55696</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>56795</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>55848</v>
       </c>
     </row>
@@ -1913,63 +1979,66 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>126420</v>
+      </c>
+      <c r="C23" t="n">
         <v>129950</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>128740</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>124545</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>119866</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>132962</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>133280</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>139395</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>145441</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>149801</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>149927</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>152734</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>148329</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>155755</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>161685</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>157806</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>161595</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>155323</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>149744</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>145881</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>148926</v>
       </c>
     </row>
@@ -1980,63 +2049,66 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>275746</v>
+      </c>
+      <c r="C24" t="n">
         <v>264591</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>291107</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>265665</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>264437</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>277327</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>264904</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>263217</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>279414</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>274764</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>270002</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>290020</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>278202</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>283263</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>309259</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>265560</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>267980</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>287830</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>245062</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>241975</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>251087</v>
       </c>
     </row>
@@ -2047,63 +2119,66 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>100702</v>
+      </c>
+      <c r="C25" t="n">
         <v>99507</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>95221</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>89806</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>88711</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>84768</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>79850</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>78815</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>75236</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>70667</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>69568</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>66399</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>62115</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>61181</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>58424</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>54989</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>54203</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>51744</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>48696</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>48032</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>45972</v>
       </c>
     </row>
@@ -2114,63 +2189,66 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>11326</v>
+      </c>
+      <c r="C26" t="n">
         <v>12359</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>-2177</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>-17607</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>-15552</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>-11221</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>-4726</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>4339</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>8242</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>1408</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>4336</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>3240</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>5289</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>12712</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>14435</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>9233</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>15261</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>14301</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>24136</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>33182</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>43977</v>
       </c>
     </row>
@@ -2181,63 +2259,66 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>-4508</v>
+      </c>
+      <c r="C27" t="n">
         <v>-5375</v>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>-4854</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>-6369</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>-6363</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>-6789</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>-8416</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>-8960</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>-9378</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>-11801</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>-11746</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>-12912</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>-9297</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>-6494</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>-927</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>58</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>-286</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>179</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>-550</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>-2789</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>-418</v>
       </c>
     </row>
@@ -2248,63 +2329,66 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>107520</v>
+      </c>
+      <c r="C28" t="n">
         <v>106491</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>88190</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>65830</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>66796</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>66758</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>66708</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>74194</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>74100</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>60274</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>62158</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>56727</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>58107</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>67399</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>71932</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>64280</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>69178</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>66224</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>72282</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>78425</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>89531</v>
       </c>
     </row>
@@ -2319,68 +2403,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46109</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>46018</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45836</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45745</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45654</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45472</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45381</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45290</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45108</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45017</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44926</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44737</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44646</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44555</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44373</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44282</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44191</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44009</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43918</v>
       </c>
-      <c r="U1" s="1" t="n">
+      <c r="V1" s="1" t="n">
         <v>43827</v>
       </c>
     </row>
@@ -2391,63 +2478,66 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>109417</v>
+      </c>
+      <c r="C2" t="n">
         <v>111184</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>143756</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>94036</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>95359</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>124300</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>85777</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>90753</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>119575</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>81797</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>94836</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>117154</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>82959</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>97278</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>123945</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>81434</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>89584</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>111439</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>59685</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>58313</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>91819</v>
       </c>
     </row>
@@ -2458,63 +2548,66 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>54647</v>
+      </c>
+      <c r="C3" t="n">
         <v>56403</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>74525</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>50318</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>50492</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>66025</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>46099</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>48482</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>64720</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>45384</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>52860</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>66822</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>47074</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>54719</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>69702</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>46179</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>51505</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>67111</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>37005</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>35943</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>56602</v>
       </c>
     </row>
@@ -2525,63 +2618,66 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>54770</v>
+      </c>
+      <c r="C4" t="n">
         <v>54781</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>69231</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>43718</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>44867</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>58275</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>39678</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>42271</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>54855</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>36413</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>41976</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>50332</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>35885</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>42559</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>54243</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>35255</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>38079</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>44328</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>22680</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>22370</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>35217</v>
       </c>
     </row>
@@ -2592,63 +2688,66 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>11729</v>
+      </c>
+      <c r="C5" t="n">
         <v>11419</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>10887</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>8866</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>8550</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>8268</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>8006</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>7903</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>7696</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>7442</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>7457</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>7709</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>6797</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>6387</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>6306</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>5717</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>5262</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>5163</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>4758</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>4565</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>4451</v>
       </c>
     </row>
@@ -2659,63 +2758,66 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>7346</v>
+      </c>
+      <c r="C6" t="n">
         <v>7477</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>7492</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>6650</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>6728</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>7175</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>6320</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>6468</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>6786</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>5973</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>6201</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>6607</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>6012</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>6193</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>6449</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>5412</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>5314</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>5631</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>4831</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>4952</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>5197</v>
       </c>
     </row>
@@ -2726,63 +2828,66 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>19075</v>
+      </c>
+      <c r="C7" t="n">
         <v>18896</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>18379</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>15516</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>15278</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>15443</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>14326</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>14371</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>14482</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>13415</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>13658</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>14316</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>12809</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>12580</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>12755</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>11129</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>10576</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>10794</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>9589</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>9517</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>9648</v>
       </c>
     </row>
@@ -2793,63 +2898,66 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>35695</v>
+      </c>
+      <c r="C8" t="n">
         <v>35885</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>50852</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>28202</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>29589</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>42832</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>25352</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>27900</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>40373</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>22998</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>28318</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>36016</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>23076</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>29979</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>41488</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>24126</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>27503</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>33534</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>13091</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>12853</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>25569</v>
       </c>
     </row>
@@ -2860,63 +2968,66 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>572</v>
+      </c>
+      <c r="C9" t="n">
         <v>-52</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>150</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>-171</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>-279</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>-248</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>142</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>158</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>-50</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>-265</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>64</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>-393</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>-10</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>160</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>-247</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>243</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>508</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>45</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>46</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>282</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>349</v>
       </c>
     </row>
@@ -2927,63 +3038,66 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>36267</v>
+      </c>
+      <c r="C10" t="n">
         <v>35833</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>51002</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>28031</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>29310</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>42584</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>25494</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>28058</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>40323</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>22733</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>28382</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>35623</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>23066</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>30139</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>41241</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>24369</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>28011</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>33579</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>13137</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>13135</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>25918</v>
       </c>
     </row>
@@ -2994,63 +3108,66 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>6478</v>
+      </c>
+      <c r="C11" t="n">
         <v>6255</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>8905</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>4597</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>4530</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>6254</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>4046</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>4422</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>6407</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>2852</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>4222</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>5625</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>3624</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>5129</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>6611</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>2625</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>4381</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>4824</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>1884</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>1886</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>3682</v>
       </c>
     </row>
@@ -3061,63 +3178,66 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>29789</v>
+      </c>
+      <c r="C12" t="n">
         <v>29578</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>42097</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>23434</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>24780</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>36330</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>21448</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>23636</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>33916</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>19881</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>24160</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>29998</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>19442</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>25010</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>34630</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>21744</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>23630</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>28755</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>11253</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>11249</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>22236</v>
       </c>
     </row>
@@ -3128,63 +3248,66 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="C13" t="n">
         <v>2.02</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>2.85</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>1.57</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>1.65</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>2.41</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>1.4</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>1.53</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>2.19</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>1.27</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>1.53</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>1.89</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>1.2</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>1.54</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>2.11</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>1.31</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>1.41</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>1.7</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>2.61</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>2.58</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>5.04</v>
       </c>
     </row>
@@ -3195,63 +3318,66 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="C14" t="n">
         <v>2.01</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>2.84</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>1.57</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>1.65</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>2.4</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>1.4</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>1.53</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>2.18</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>1.26</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>1.52</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>1.88</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>1.2</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>1.52</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>2.1</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>1.4</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>1.68</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>2.58</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>2.55</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>4.99</v>
       </c>
     </row>
@@ -3262,63 +3388,66 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>14656110</v>
+      </c>
+      <c r="C15" t="n">
         <v>14673278</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>14748158</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>14902886</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>14994082</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>15081724</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>15287521</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>15405856</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>15509763</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>15697614</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>15787154</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>15892723</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>16162945</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>16278802</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>16391724</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>16629371</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>16753476</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>16935119</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>4312573</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>4360101</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>4415040</v>
       </c>
     </row>
@@ -3329,63 +3458,66 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>14714676</v>
+      </c>
+      <c r="C16" t="n">
         <v>14725873</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>14810356</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>14948179</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>15056133</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>15150865</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>15348175</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>15464709</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>15576641</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>15775021</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>15847050</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>15955718</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16262203</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>16403316</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>16519291</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>16781735</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>16929157</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>17113688</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>4354788</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>4404691</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>4454604</v>
       </c>
     </row>
@@ -3400,68 +3532,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U37"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46109</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>46018</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45836</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45745</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45654</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45472</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45381</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45290</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45108</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45017</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44926</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44737</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44646</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44555</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44373</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44282</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44191</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44009</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43918</v>
       </c>
-      <c r="U1" s="1" t="n">
+      <c r="V1" s="1" t="n">
         <v>43827</v>
       </c>
     </row>
@@ -3478,7 +3613,7 @@
         <v>35934</v>
       </c>
       <c r="D2" t="n">
-        <v>29943</v>
+        <v>35934</v>
       </c>
       <c r="E2" t="n">
         <v>29943</v>
@@ -3487,7 +3622,7 @@
         <v>29943</v>
       </c>
       <c r="G2" t="n">
-        <v>30737</v>
+        <v>29943</v>
       </c>
       <c r="H2" t="n">
         <v>30737</v>
@@ -3496,7 +3631,7 @@
         <v>30737</v>
       </c>
       <c r="J2" t="n">
-        <v>24977</v>
+        <v>30737</v>
       </c>
       <c r="K2" t="n">
         <v>24977</v>
@@ -3505,7 +3640,7 @@
         <v>24977</v>
       </c>
       <c r="M2" t="n">
-        <v>35929</v>
+        <v>24977</v>
       </c>
       <c r="N2" t="n">
         <v>35929</v>
@@ -3514,7 +3649,7 @@
         <v>35929</v>
       </c>
       <c r="P2" t="n">
-        <v>39789</v>
+        <v>35929</v>
       </c>
       <c r="Q2" t="n">
         <v>39789</v>
@@ -3523,7 +3658,7 @@
         <v>39789</v>
       </c>
       <c r="S2" t="n">
-        <v>50224</v>
+        <v>39789</v>
       </c>
       <c r="T2" t="n">
         <v>50224</v>
@@ -3531,6 +3666,9 @@
       <c r="U2" t="n">
         <v>50224</v>
       </c>
+      <c r="V2" t="n">
+        <v>50224</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3539,63 +3677,66 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>101464</v>
+      </c>
+      <c r="C3" t="n">
         <v>71675</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>42097</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>84544</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>61110</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>36330</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>79000</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>57552</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>33916</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>74039</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>54158</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>29998</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>79082</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>59640</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>34630</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>74129</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>52385</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>28755</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>44738</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>33485</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>22236</v>
       </c>
     </row>
@@ -3606,63 +3747,66 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>9973</v>
+      </c>
+      <c r="C4" t="n">
         <v>6653</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>3214</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>8571</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>5741</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>3080</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>8534</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>5684</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>2848</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>8866</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5814</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>2916</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>8239</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>5434</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>2697</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>8295</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>5463</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>2666</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>8354</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>5602</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>2816</v>
       </c>
     </row>
@@ -3673,63 +3817,66 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>10523</v>
+      </c>
+      <c r="C5" t="n">
         <v>7122</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>3594</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>9680</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>6512</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>3286</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>8830</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>5961</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>2997</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>8208</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>5591</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>2905</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>6760</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>4517</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>2265</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>5961</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>4001</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>2020</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5105</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>3407</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>1710</v>
       </c>
     </row>
@@ -3740,63 +3887,66 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>-2037</v>
+      </c>
+      <c r="C6" t="n">
         <v>-1717</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>-528</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>-1748</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>-2217</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>-2009</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>-1964</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>-1971</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>-989</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>-1651</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>-1732</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>-317</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>-61</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>-20</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>167</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>-689</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>-474</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>25</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>-94</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>-259</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>-142</v>
       </c>
     </row>
@@ -3807,63 +3957,66 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>8316</v>
+      </c>
+      <c r="C7" t="n">
         <v>9295</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>-153</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>5685</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>7266</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>3597</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>6697</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>7727</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>6555</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>7609</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>9596</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>4275</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>4561</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>5542</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>-3934</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>-1316</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>-2347</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>-10945</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>5149</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>7284</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3874,63 +4027,66 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>5671</v>
+      </c>
+      <c r="C8" t="n">
         <v>10008</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>2781</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>13555</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>9171</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>3166</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>11100</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>12164</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>4569</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>13111</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>14785</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>2320</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>4789</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>643</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>-9812</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>4892</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>6792</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>-10194</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>8685</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>7923</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>3902</v>
       </c>
     </row>
@@ -3941,63 +4097,66 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>-5461</v>
+      </c>
+      <c r="C9" t="n">
         <v>-1084</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>-211</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>1223</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>858</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>215</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>41</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>53</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>-137</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>-2570</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>-2548</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>-1807</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>1049</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>1065</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>681</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>-1213</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>-1226</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>-950</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>10</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>699</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>-28</v>
       </c>
     </row>
@@ -4008,63 +4167,66 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>-16266</v>
+      </c>
+      <c r="C10" t="n">
         <v>-14329</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>-10250</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>-6116</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>-4371</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>939</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>-5626</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>-4438</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>-1457</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>-4863</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>-4092</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>-4099</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>-3289</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>-3542</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>-4921</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>-5899</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>-4333</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>-3526</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>-6760</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>-8866</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>-7054</v>
       </c>
     </row>
@@ -4075,63 +4237,66 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>-5203</v>
+      </c>
+      <c r="C11" t="n">
         <v>-12297</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>848</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>-18479</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>-14604</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>-6671</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>-15171</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>-16710</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>-4542</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>-16790</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>-20764</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>-6075</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>-6108</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>-1750</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>19813</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>-1786</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>-1997</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>21670</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>-10787</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>-13520</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>-1089</v>
       </c>
     </row>
@@ -4142,63 +4307,66 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>10016</v>
+      </c>
+      <c r="C12" t="n">
         <v>7301</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>12533</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>-15161</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>-15579</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>-11998</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>2</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>-3437</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>-3865</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>2986</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>1757</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>3758</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>-14</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>1888</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>4236</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>463</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>3045</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>7959</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>3867</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>7500</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>5514</v>
       </c>
     </row>
@@ -4209,63 +4377,66 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>116996</v>
+      </c>
+      <c r="C13" t="n">
         <v>82627</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>53925</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>81754</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>53887</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>29935</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>91443</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>62585</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>39895</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>88945</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>62565</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>34005</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>98024</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>75132</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>46966</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>83838</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>62744</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>38763</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>60098</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>43827</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>30516</v>
       </c>
     </row>
@@ -4276,63 +4447,66 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>-48752</v>
+      </c>
+      <c r="C14" t="n">
         <v>-32432</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>-12693</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>-17591</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>-12442</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>-6124</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>-38074</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>-25042</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>-9780</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>-20956</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>-11197</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>-5153</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>-70178</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>-61987</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>-34913</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>-94052</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>-74424</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>-39800</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>-96606</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>-66489</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>-37416</v>
       </c>
     </row>
@@ -4343,63 +4517,66 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>26504</v>
+      </c>
+      <c r="C15" t="n">
         <v>18691</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>7510</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>35036</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>26587</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>15967</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>39838</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>27462</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>13046</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>27857</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>17124</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>7127</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>24203</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>18000</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>11309</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>49880</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>39605</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>25177</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>54865</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>39738</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>19740</v>
       </c>
     </row>
@@ -4410,63 +4587,66 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>12016</v>
+      </c>
+      <c r="C16" t="n">
         <v>8615</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>2824</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>10785</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>5210</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>3492</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>7382</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>4314</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>1337</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>3959</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>1897</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>509</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>33609</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>24668</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>10675</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>36745</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>21645</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>9344</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>39760</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>27762</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>7280</v>
       </c>
     </row>
@@ -4477,63 +4657,66 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>-6799</v>
+      </c>
+      <c r="C17" t="n">
         <v>-4344</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>-2373</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>-9473</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>-6011</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>-2940</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>-6539</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>-4388</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>-2392</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>-8796</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>-6703</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>-3787</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>-7419</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>-5317</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>-2803</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>-7862</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>-5769</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>-3500</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>-5525</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>-3960</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>-2107</v>
       </c>
     </row>
@@ -4544,63 +4727,66 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>-1780</v>
+      </c>
+      <c r="C18" t="n">
         <v>-1584</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>-154</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>-975</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>-635</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>-603</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>-1117</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>-729</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>-284</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>-753</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>-247</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>-141</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>-1183</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>-568</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>-374</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>-78</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>204</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>-689</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>-426</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>-130</v>
       </c>
     </row>
@@ -4611,63 +4797,66 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>-18811</v>
+      </c>
+      <c r="C19" t="n">
         <v>-11054</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>-4886</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>17782</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>12709</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>9792</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>1490</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>1617</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1927</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>1311</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>874</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>-1445</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>-21137</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>-25371</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>-16106</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>-15380</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>-18952</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>-8584</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>-9820</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>-4655</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>-13668</v>
       </c>
     </row>
@@ -4678,63 +4867,66 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>-6462</v>
+      </c>
+      <c r="C20" t="n">
         <v>-3252</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>-2922</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>-5719</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>-3205</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>-2921</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>-5163</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>-2875</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>-2591</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>-5119</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>-2734</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>-2316</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>-5915</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>-3218</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>-2888</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>-5855</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>-3160</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>-2861</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>-3234</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>-1566</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>-1379</v>
       </c>
     </row>
@@ -4745,63 +4937,66 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>-11778</v>
+      </c>
+      <c r="C21" t="n">
         <v>-7743</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>-3921</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>-11559</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>-7614</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>-3856</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>-11430</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>-7535</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>-3825</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>-11267</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>-7418</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>-3768</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>-11138</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>-7327</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>-3732</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>-10827</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>-7060</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>-3613</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>-10570</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>-6914</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>-3539</v>
       </c>
     </row>
@@ -4812,533 +5007,557 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>-62094</v>
+      </c>
+      <c r="C22" t="n">
         <v>-36989</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>-24701</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>-70579</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>-49504</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>-23606</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>-69866</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>-43344</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>-20139</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>-56547</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>-39069</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>-19475</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>-64974</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>-43109</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>-20478</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>-66223</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>-43323</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>-24775</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>-55171</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>-39280</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>-20706</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Repayments of Long-term Debt</t>
+          <t>Proceeds from Issuance of Long-term Debt</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-7914</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>-2164</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-9682</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>-4009</v>
+        <v>4481</v>
       </c>
       <c r="F23" t="n">
-        <v>-1009</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>-7400</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-3150</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>-11151</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>-3651</v>
+        <v>5228</v>
       </c>
       <c r="L23" t="n">
-        <v>-1401</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-6750</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-3750</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-7500</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4500</v>
+        <v>13923</v>
       </c>
       <c r="R23" t="n">
-        <v>-1000</v>
+        <v>13923</v>
       </c>
       <c r="S23" t="n">
-        <v>-12629</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>-5250</v>
+        <v>10635</v>
       </c>
       <c r="U23" t="n">
-        <v>-1000</v>
+        <v>2210</v>
+      </c>
+      <c r="V23" t="n">
+        <v>2210</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from (Repayments of) Commercial Paper</t>
+          <t>Repayments of Long-term Debt</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-5911</v>
+        <v>-8146</v>
       </c>
       <c r="C24" t="n">
-        <v>-5910</v>
+        <v>-7914</v>
       </c>
       <c r="D24" t="n">
-        <v>-65</v>
+        <v>-2164</v>
       </c>
       <c r="E24" t="n">
-        <v>-3968</v>
+        <v>-9682</v>
       </c>
       <c r="F24" t="n">
-        <v>-7944</v>
+        <v>-4009</v>
       </c>
       <c r="G24" t="n">
-        <v>-2985</v>
+        <v>-1009</v>
       </c>
       <c r="H24" t="n">
-        <v>-3982</v>
+        <v>-7400</v>
       </c>
       <c r="I24" t="n">
-        <v>-3984</v>
+        <v>-3150</v>
       </c>
       <c r="J24" t="n">
-        <v>-5971</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>-7960</v>
+        <v>-11151</v>
       </c>
       <c r="L24" t="n">
-        <v>-8214</v>
+        <v>-3651</v>
       </c>
       <c r="M24" t="n">
-        <v>4970</v>
+        <v>-1401</v>
       </c>
       <c r="N24" t="n">
-        <v>999</v>
+        <v>-6750</v>
       </c>
       <c r="O24" t="n">
+        <v>-3750</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-7500</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-4500</v>
+      </c>
+      <c r="S24" t="n">
         <v>-1000</v>
       </c>
-      <c r="P24" t="n">
-        <v>3022</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>22</v>
-      </c>
-      <c r="R24" t="n">
-        <v>22</v>
-      </c>
-      <c r="S24" t="n">
-        <v>31</v>
-      </c>
       <c r="T24" t="n">
-        <v>1518</v>
+        <v>-12629</v>
       </c>
       <c r="U24" t="n">
-        <v>-979</v>
+        <v>-5250</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-1000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from (Payments for) Other Financing Activities</t>
+          <t>Proceeds from (Repayments of) Commercial Paper</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-126</v>
+        <v>-5911</v>
       </c>
       <c r="C25" t="n">
-        <v>-38</v>
+        <v>-5911</v>
       </c>
       <c r="D25" t="n">
-        <v>-87</v>
+        <v>-5910</v>
       </c>
       <c r="E25" t="n">
-        <v>-77</v>
+        <v>-65</v>
       </c>
       <c r="F25" t="n">
-        <v>-35</v>
+        <v>-3968</v>
       </c>
       <c r="G25" t="n">
-        <v>-191</v>
+        <v>-7944</v>
       </c>
       <c r="H25" t="n">
-        <v>-132</v>
+        <v>-2985</v>
       </c>
       <c r="I25" t="n">
-        <v>-46</v>
+        <v>-3982</v>
       </c>
       <c r="J25" t="n">
-        <v>-508</v>
+        <v>-3984</v>
       </c>
       <c r="K25" t="n">
-        <v>-455</v>
+        <v>-5971</v>
       </c>
       <c r="L25" t="n">
-        <v>-389</v>
+        <v>-7960</v>
       </c>
       <c r="M25" t="n">
-        <v>-148</v>
+        <v>-8214</v>
       </c>
       <c r="N25" t="n">
-        <v>-105</v>
+        <v>4970</v>
       </c>
       <c r="O25" t="n">
-        <v>-61</v>
+        <v>999</v>
       </c>
       <c r="P25" t="n">
-        <v>-72</v>
+        <v>-1000</v>
       </c>
       <c r="Q25" t="n">
-        <v>-38</v>
+        <v>3022</v>
       </c>
       <c r="R25" t="n">
-        <v>-22</v>
+        <v>22</v>
       </c>
       <c r="S25" t="n">
-        <v>-120</v>
+        <v>22</v>
       </c>
       <c r="T25" t="n">
-        <v>-51</v>
+        <v>31</v>
       </c>
       <c r="U25" t="n">
-        <v>-16</v>
+        <v>1518</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-979</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Net Cash Provided by (Used in) Financing Activities</t>
+          <t>Proceeds from (Payments for) Other Financing Activities</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-61935</v>
+        <v>-184</v>
       </c>
       <c r="C26" t="n">
-        <v>-39656</v>
+        <v>-126</v>
       </c>
       <c r="D26" t="n">
-        <v>-93210</v>
+        <v>-38</v>
       </c>
       <c r="E26" t="n">
-        <v>-68377</v>
+        <v>-87</v>
       </c>
       <c r="F26" t="n">
-        <v>-39371</v>
+        <v>-77</v>
       </c>
       <c r="G26" t="n">
-        <v>-97035</v>
+        <v>-35</v>
       </c>
       <c r="H26" t="n">
-        <v>-61018</v>
+        <v>-191</v>
       </c>
       <c r="I26" t="n">
-        <v>-30585</v>
+        <v>-132</v>
       </c>
       <c r="J26" t="n">
-        <v>-85335</v>
+        <v>-46</v>
       </c>
       <c r="K26" t="n">
-        <v>-61287</v>
+        <v>-508</v>
       </c>
       <c r="L26" t="n">
-        <v>-35563</v>
+        <v>-455</v>
       </c>
       <c r="M26" t="n">
-        <v>-83955</v>
+        <v>-389</v>
       </c>
       <c r="N26" t="n">
-        <v>-56510</v>
+        <v>-148</v>
       </c>
       <c r="O26" t="n">
-        <v>-28159</v>
+        <v>-105</v>
       </c>
       <c r="P26" t="n">
-        <v>-72971</v>
+        <v>-61</v>
       </c>
       <c r="Q26" t="n">
-        <v>-43575</v>
+        <v>-72</v>
       </c>
       <c r="R26" t="n">
-        <v>-32249</v>
+        <v>-38</v>
       </c>
       <c r="S26" t="n">
-        <v>-65463</v>
+        <v>-22</v>
       </c>
       <c r="T26" t="n">
-        <v>-46347</v>
+        <v>-120</v>
       </c>
       <c r="U26" t="n">
-        <v>-25407</v>
+        <v>-51</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Period Increase (Decrease), Including Exchange Rate Effect</t>
+          <t>Net Cash Provided by (Used in) Financing Activities</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9638</v>
+        <v>-94575</v>
       </c>
       <c r="C27" t="n">
-        <v>9383</v>
+        <v>-61935</v>
       </c>
       <c r="D27" t="n">
-        <v>6326</v>
+        <v>-39656</v>
       </c>
       <c r="E27" t="n">
-        <v>-1781</v>
+        <v>-93210</v>
       </c>
       <c r="F27" t="n">
-        <v>356</v>
+        <v>-68377</v>
       </c>
       <c r="G27" t="n">
-        <v>-4102</v>
+        <v>-39371</v>
       </c>
       <c r="H27" t="n">
-        <v>3184</v>
+        <v>-97035</v>
       </c>
       <c r="I27" t="n">
-        <v>11237</v>
+        <v>-61018</v>
       </c>
       <c r="J27" t="n">
-        <v>4921</v>
+        <v>-30585</v>
       </c>
       <c r="K27" t="n">
-        <v>2152</v>
+        <v>-85335</v>
       </c>
       <c r="L27" t="n">
-        <v>-3003</v>
+        <v>-61287</v>
       </c>
       <c r="M27" t="n">
-        <v>-7068</v>
+        <v>-35563</v>
       </c>
       <c r="N27" t="n">
-        <v>-6749</v>
+        <v>-83955</v>
       </c>
       <c r="O27" t="n">
-        <v>2701</v>
+        <v>-56510</v>
       </c>
       <c r="P27" t="n">
-        <v>-4513</v>
+        <v>-28159</v>
       </c>
       <c r="Q27" t="n">
-        <v>217</v>
+        <v>-72971</v>
       </c>
       <c r="R27" t="n">
-        <v>-2070</v>
+        <v>-43575</v>
       </c>
       <c r="S27" t="n">
-        <v>-15185</v>
+        <v>-32249</v>
       </c>
       <c r="T27" t="n">
-        <v>-7175</v>
+        <v>-65463</v>
       </c>
       <c r="U27" t="n">
-        <v>-8559</v>
+        <v>-46347</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-25407</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Income Taxes Paid, Net</t>
+          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Period Increase (Decrease), Including Exchange Rate Effect</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>20397</v>
+        <v>3610</v>
       </c>
       <c r="C28" t="n">
-        <v>3434</v>
+        <v>9638</v>
       </c>
       <c r="D28" t="n">
-        <v>37332</v>
+        <v>9383</v>
       </c>
       <c r="E28" t="n">
-        <v>31683</v>
+        <v>6326</v>
       </c>
       <c r="F28" t="n">
-        <v>18651</v>
+        <v>-1781</v>
       </c>
       <c r="G28" t="n">
-        <v>19230</v>
+        <v>356</v>
       </c>
       <c r="H28" t="n">
-        <v>14531</v>
+        <v>-4102</v>
       </c>
       <c r="I28" t="n">
-        <v>7255</v>
+        <v>3184</v>
       </c>
       <c r="J28" t="n">
-        <v>7020</v>
+        <v>11237</v>
       </c>
       <c r="K28" t="n">
-        <v>4894</v>
+        <v>4921</v>
       </c>
       <c r="L28" t="n">
-        <v>828</v>
+        <v>2152</v>
       </c>
       <c r="M28" t="n">
-        <v>12251</v>
+        <v>-3003</v>
       </c>
       <c r="N28" t="n">
-        <v>9301</v>
+        <v>-7068</v>
       </c>
       <c r="O28" t="n">
-        <v>5235</v>
+        <v>-6749</v>
       </c>
       <c r="P28" t="n">
-        <v>18536</v>
+        <v>2701</v>
       </c>
       <c r="Q28" t="n">
-        <v>10276</v>
+        <v>-4513</v>
       </c>
       <c r="R28" t="n">
-        <v>1787</v>
+        <v>217</v>
       </c>
       <c r="S28" t="n">
-        <v>8410</v>
+        <v>-2070</v>
       </c>
       <c r="T28" t="n">
-        <v>7505</v>
+        <v>-15185</v>
       </c>
       <c r="U28" t="n">
-        <v>4393</v>
+        <v>-7175</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-8559</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Issuance of Long-term Debt</t>
+          <t>Income Taxes Paid, Net</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>26555</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>20397</v>
       </c>
       <c r="D29" t="n">
-        <v>4481</v>
+        <v>3434</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>37332</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>31683</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>18651</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>19230</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>14531</v>
       </c>
       <c r="J29" t="n">
-        <v>5228</v>
+        <v>7255</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>7020</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>4894</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>828</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>12251</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>9301</v>
       </c>
       <c r="P29" t="n">
-        <v>13923</v>
+        <v>5235</v>
       </c>
       <c r="Q29" t="n">
-        <v>13923</v>
+        <v>18536</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>10276</v>
       </c>
       <c r="S29" t="n">
-        <v>10635</v>
+        <v>1787</v>
       </c>
       <c r="T29" t="n">
-        <v>2210</v>
+        <v>8410</v>
       </c>
       <c r="U29" t="n">
-        <v>2210</v>
+        <v>7505</v>
+      </c>
+      <c r="V29" t="n">
+        <v>4393</v>
       </c>
     </row>
     <row r="30">
@@ -5372,39 +5591,42 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>2590</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1873</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>703</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>1910</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>1406</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>531</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>1870</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>1327</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>619</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>2275</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>1689</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>771</v>
       </c>
     </row>
@@ -5445,33 +5667,36 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>131</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>260</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>627</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>462</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>1738</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>1642</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>1341</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>1649</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>1223</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>985</v>
       </c>
     </row>
@@ -5515,30 +5740,33 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
         <v>2756</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>1088</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>682</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>-737</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>-207</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>-58</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>182</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>-651</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>-349</v>
       </c>
     </row>
@@ -5582,30 +5810,33 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>-169</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>-167</v>
       </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
       <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>-13</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>-9</v>
       </c>
       <c r="R33" t="n">
         <v>-9</v>
       </c>
       <c r="S33" t="n">
+        <v>-9</v>
+      </c>
+      <c r="T33" t="n">
         <v>-1473</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>-1134</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>-958</v>
       </c>
     </row>
@@ -5658,21 +5889,24 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>561</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>561</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>561</v>
       </c>
       <c r="S34" t="n">
-        <v>430</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>430</v>
       </c>
       <c r="U34" t="n">
+        <v>430</v>
+      </c>
+      <c r="V34" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5734,12 +5968,15 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
         <v>5165</v>
       </c>
-      <c r="T35" t="n">
+      <c r="U35" t="n">
         <v>2556</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5801,12 +6038,15 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
         <v>-210</v>
       </c>
-      <c r="T36" t="n">
+      <c r="U36" t="n">
         <v>-146</v>
       </c>
-      <c r="U36" t="n">
+      <c r="V36" t="n">
         <v>-77</v>
       </c>
     </row>
@@ -5868,12 +6108,15 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
         <v>58</v>
       </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
       <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5893,7 +6136,7 @@
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
-        <v>46109</v>
+        <v>46200</v>
       </c>
     </row>
     <row r="2">
@@ -5903,7 +6146,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>173985</v>
+        <v>143962</v>
       </c>
     </row>
   </sheetData>
